--- a/IPPU/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
+++ b/IPPU/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\IPPU\A2_Extra_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\IPPU_hfc_desglose\A2_Extra_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715E9EB3-4D8D-421B-B046-51350050EE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9B23CC-31BC-467C-AF80-A132A4CFF678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GHGs" sheetId="1" r:id="rId1"/>
     <sheet name="Externalities" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GHGs!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GHGs!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="38">
   <si>
     <t>External Cost</t>
   </si>
@@ -81,18 +81,6 @@
     <t>OTHER_IPPU</t>
   </si>
   <si>
-    <t>CO2e_leakage</t>
-  </si>
-  <si>
-    <t>0.15 of consumption</t>
-  </si>
-  <si>
-    <t>0.85 of consumption</t>
-  </si>
-  <si>
-    <t>CO2e_consumption_com</t>
-  </si>
-  <si>
     <t>IMP_HFC23</t>
   </si>
   <si>
@@ -136,6 +124,33 @@
   </si>
   <si>
     <t>PARAFFIN</t>
+  </si>
+  <si>
+    <t>MtCO2eq/MtCO2eq</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC23</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC32</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC125</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC134a</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC143a</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC152a</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC227ea</t>
+  </si>
+  <si>
+    <t>Este gas está fuera de la categoria 2F1 por lo que no tiene actividad</t>
   </si>
 </sst>
 </file>
@@ -168,7 +183,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -213,18 +228,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -300,15 +309,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -403,17 +403,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -422,30 +411,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -528,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -539,48 +504,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -866,17 +822,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -887,11 +843,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6">
@@ -901,344 +857,249 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="29">
+        <v>12.4</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="29">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="29">
+        <v>3.17</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="29">
+        <v>1.3</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="16">
+      <c r="B7" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="29">
+        <v>4.8</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="29">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="30">
+        <v>3.35</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="16">
+      <c r="D10" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="19">
+        <v>0.52029999999999998</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="8">
         <v>1</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="16">
+      <c r="D12" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="21">
         <v>1</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="16">
+      <c r="D13" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="21">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="16">
+      <c r="D14" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="21">
         <v>1</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="16">
+      <c r="D15" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="21">
         <v>1</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="17">
+      <c r="D16" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="21">
         <v>1</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="18">
+      <c r="D17" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="21">
         <v>1</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="16">
+      <c r="D18" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="22">
         <v>1</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="16">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="16">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="16">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="16">
-        <v>1</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="19">
-        <v>1</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="28">
-        <v>0.52029999999999998</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="8">
-        <v>1</v>
-      </c>
       <c r="D19" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="30">
-        <v>1</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="30">
-        <v>1</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="30">
-        <v>1</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="30">
-        <v>1</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="30">
-        <v>1</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="30">
-        <v>1</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="31">
-        <v>1</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C11" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1282,21 +1143,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="314e7041d7d1561dbe33e80becf1c782">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84c838da6aa04a0f137f8b0aba02cfe1" ns2:_="">
     <xsd:import namespace="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
@@ -1466,15 +1318,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69F79AB8-49D9-484F-991A-27FAE0E62C64}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFFB2CC7-4028-40CF-B585-77900DA351B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1484,7 +1337,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E70820A0-1361-44AE-AADB-917A2734D25C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1500,4 +1353,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69F79AB8-49D9-484F-991A-27FAE0E62C64}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>